--- a/artfynd/A 39619-2026 artfynd.xlsx
+++ b/artfynd/A 39619-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1008,6 +1008,127 @@
       <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/75360581</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137282817</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98262</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Riddarhyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>527893</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6629933</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137282817</t>
         </is>
       </c>
     </row>
@@ -1016,6 +1137,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39619-2026 artfynd.xlsx
+++ b/artfynd/A 39619-2026 artfynd.xlsx
@@ -1016,7 +1016,7 @@
         <v>137282817</v>
       </c>
       <c r="B5" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39619-2026 artfynd.xlsx
+++ b/artfynd/A 39619-2026 artfynd.xlsx
@@ -1016,7 +1016,7 @@
         <v>137282817</v>
       </c>
       <c r="B5" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39619-2026 artfynd.xlsx
+++ b/artfynd/A 39619-2026 artfynd.xlsx
@@ -1016,7 +1016,7 @@
         <v>137282817</v>
       </c>
       <c r="B5" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39619-2026 artfynd.xlsx
+++ b/artfynd/A 39619-2026 artfynd.xlsx
@@ -1016,7 +1016,7 @@
         <v>137282817</v>
       </c>
       <c r="B5" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39619-2026 artfynd.xlsx
+++ b/artfynd/A 39619-2026 artfynd.xlsx
@@ -1016,7 +1016,7 @@
         <v>137282817</v>
       </c>
       <c r="B5" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39619-2026 artfynd.xlsx
+++ b/artfynd/A 39619-2026 artfynd.xlsx
@@ -1016,7 +1016,7 @@
         <v>137282817</v>
       </c>
       <c r="B5" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39619-2026 artfynd.xlsx
+++ b/artfynd/A 39619-2026 artfynd.xlsx
@@ -1016,7 +1016,7 @@
         <v>137282817</v>
       </c>
       <c r="B5" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39619-2026 artfynd.xlsx
+++ b/artfynd/A 39619-2026 artfynd.xlsx
@@ -1016,7 +1016,7 @@
         <v>137282817</v>
       </c>
       <c r="B5" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39619-2026 artfynd.xlsx
+++ b/artfynd/A 39619-2026 artfynd.xlsx
@@ -1016,7 +1016,7 @@
         <v>137282817</v>
       </c>
       <c r="B5" t="n">
-        <v>98302</v>
+        <v>98306</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
